--- a/docs/gantt.xlsx
+++ b/docs/gantt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\di913\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9B3B497-1F3F-48E0-8E9E-FA6129480773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FB878D-EC07-4334-855A-7353F17B4D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2550" yWindow="2550" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Гантт" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
   <si>
     <t>Занятие</t>
   </si>
@@ -167,6 +167,9 @@
   </si>
   <si>
     <t>Ильин Данил, Ахмадиев Ильяс</t>
+  </si>
+  <si>
+    <t>сделано</t>
   </si>
 </sst>
 </file>
@@ -256,12 +259,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -574,20 +577,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -620,7 +623,7 @@
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -637,7 +640,7 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -831,7 +834,7 @@
       <c r="A19" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="5" t="s">
         <v>48</v>
       </c>
     </row>
